--- a/inventory.xlsx
+++ b/inventory.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a45cc3699792be64/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\errop\aws_inventory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1F66D8EE-C5EB-4DA7-9EFF-D3F0E568F645}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B843B88D-8D5F-4D3B-AE23-52C98282B8AD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7930" xr2:uid="{062FBF7F-E507-4C39-941B-5A744C0083F2}"/>
   </bookViews>
@@ -460,7 +460,7 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>8080</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -480,7 +480,7 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>8080</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
@@ -500,7 +500,7 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>8080</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>

--- a/inventory.xlsx
+++ b/inventory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\errop\aws_inventory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B843B88D-8D5F-4D3B-AE23-52C98282B8AD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C9907BF-2CBE-4C93-96C7-D6AB39E0D11E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7930" xr2:uid="{062FBF7F-E507-4C39-941B-5A744C0083F2}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>hostname</t>
   </si>
@@ -51,16 +51,10 @@
     <t>host2</t>
   </si>
   <si>
-    <t>host3</t>
-  </si>
-  <si>
     <t>192.168.206.130</t>
   </si>
   <si>
     <t>192.168.206.132</t>
-  </si>
-  <si>
-    <t>192.168.206.133</t>
   </si>
   <si>
     <t>admin</t>
@@ -422,7 +416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{416A45F8-15EF-4FDC-83A0-8060350604FE}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="11.7265625" customWidth="1"/>
@@ -457,19 +451,19 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2">
         <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -477,39 +471,19 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3">
         <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
         <v>11</v>
-      </c>
-      <c r="C4">
-        <v>22</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/inventory.xlsx
+++ b/inventory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\errop\aws_inventory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C9907BF-2CBE-4C93-96C7-D6AB39E0D11E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7C27C9D-476E-40A7-8525-FE934603FF5A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7930" xr2:uid="{062FBF7F-E507-4C39-941B-5A744C0083F2}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
   <si>
     <t>hostname</t>
   </si>
@@ -64,6 +64,12 @@
   </si>
   <si>
     <t>test</t>
+  </si>
+  <si>
+    <t>host3</t>
+  </si>
+  <si>
+    <t>192.168.206.133</t>
   </si>
 </sst>
 </file>
@@ -416,7 +422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{416A45F8-15EF-4FDC-83A0-8060350604FE}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="11.7265625" customWidth="1"/>
@@ -454,7 +460,7 @@
         <v>8</v>
       </c>
       <c r="C2">
-        <v>22</v>
+        <v>2211</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
@@ -483,6 +489,26 @@
         <v>10</v>
       </c>
       <c r="F3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" t="s">
         <v>11</v>
       </c>
     </row>
